--- a/output/2026-09-06_21_Slovenia_Osrednjeslovenska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-06_21_Slovenia_Osrednjeslovenska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rivenditore/importatore di macchine utensili (taglio/piegatura lamiera e tubi, presse, automazione CNC) di oltre 25 costruttori, dal 1987. Attività registrata: intermediazione commercio all'ingrosso di macchinari.</t>
+          <t>Rivenditore/importatore di macchine utensili (taglio/piegatura lamiera e tubi, presse, automazione CNC) di oltre 25 costruttori, dal 1987. Attività registrata: intermediazione commercio all'ingrosso di macchinari. [DUPLICATO — vedi anche: 2026-09-06_13_Slovenia_Posavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rivenditore e centro assistenza autorizzato per utensili elettrici professionali Makita e Flex, oltre 30 anni di attività, dal 1992.</t>
+          <t>Rivenditore e centro assistenza autorizzato per utensili elettrici professionali Makita e Flex, oltre 30 anni di attività, dal 1992. [DUPLICATO — vedi anche: 2026-09-06_08_Slovenia_Zasavska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Filiale locale di rete nazionale di forniture industriali (Beta, Bosch, SKF, componenti idraulici/pneumatici); altre filiali a Novo Mesto, Ravne na Koroškem, Koper, Vipava.</t>
+          <t>Filiale locale di rete nazionale di forniture industriali (Beta, Bosch, SKF, componenti idraulici/pneumatici); altre filiali a Novo Mesto, Ravne na Koroškem, Koper, Vipava. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -872,10 +872,9 @@
           <t>01 3649111</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Vendita, assistenza e noleggio di saldatrici; centro assistenza autorizzato per i marchi CEA, STEL, JASIC. Piccola azienda familiare dal 1990. Email non reperibile.</t>
+          <t>Vendita, assistenza e noleggio di saldatrici; centro assistenza autorizzato per i marchi CEA, STEL, JASIC. Piccola azienda familiare dal 1990. Email non reperibile. [DUPLICATO — vedi anche: 2026-09-06_13_Slovenia_Posavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -917,7 +916,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rivenditore e centro assistenza per sistemi di saldatura e taglio (rappresenta Perkeo, Weldas, Fronius, Cebora, Kemppi); sede anche a Maribor.</t>
+          <t>Rivenditore e centro assistenza per sistemi di saldatura e taglio (rappresenta Perkeo, Weldas, Fronius, Cebora, Kemppi); sede anche a Maribor. [DUPLICATO — vedi anche: 2026-09-06_10_Slovenia_Zasavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1001,7 +1000,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rappresentante/distributore Fronius (saldatura, taglio plasma), Hypertherm, Kemper, Pferd; centro assistenza autorizzato Fronius con ricambi originali.</t>
+          <t>Rappresentante/distributore Fronius (saldatura, taglio plasma), Hypertherm, Kemper, Pferd; centro assistenza autorizzato Fronius con ricambi originali. [DUPLICATO — vedi anche: 2026-09-06_10_Slovenia_Zasavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1043,7 +1042,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Produttore (oltre 350 dipendenti, dal 1988) di compressori a vite/pistone, essiccatori, filtri e generatori di azoto a marchio proprio, con vendita diretta anche tramite negozio online (trgovina.omega-air.si). E' un produttore con canale di vendita diretto, non un cliente finale.</t>
+          <t>Produttore (oltre 350 dipendenti, dal 1988) di compressori a vite/pistone, essiccatori, filtri e generatori di azoto a marchio proprio, con vendita diretta anche tramite negozio online (trgovina.omega-air.si). E' un produttore con canale di vendita diretto, non un cliente finale. [DUPLICATO — vedi anche: 2026-09-06_20_Slovenia_Osrednjeslovenska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1162,7 +1161,6 @@
           <t>01 541 18 15</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Rivenditore di viti ed elementi di fissaggio, ancoraggi, elettrodi, dischi e utensili correlati, oltre 30 anni di attività. L'azienda opera anche nel settore nautico (accessori per imbarcazioni) come seconda linea di business. Email non reperibile.</t>
@@ -1195,7 +1193,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>m-online@metaloprema.si</t>
@@ -1455,7 +1452,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Distributore ufficiale Parker per l'idraulica in Slovenia; ampio catalogo (400.000+ articoli) di pneumatica, idraulica e componenti industriali.</t>
+          <t>Distributore ufficiale Parker per l'idraulica in Slovenia; ampio catalogo (400.000+ articoli) di pneumatica, idraulica e componenti industriali. [DUPLICATO — vedi anche: 2026-09-05_22_Slovenia_Pomurska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
